--- a/dados/SURVEY_STARNAV_D2.xlsx
+++ b/dados/SURVEY_STARNAV_D2.xlsx
@@ -1545,7 +1545,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Underway</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -3505,7 +3505,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -4491,7 +4491,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -5489,7 +5489,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>under using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -8475,7 +8475,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -10471,7 +10471,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -11491,7 +11491,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>under using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -12489,7 +12489,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -13479,7 +13479,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>at anchor</t>
+          <t>At Anchor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>underway using engine</t>
+          <t>Underway using Engine</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -14487,7 +14487,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -15465,7 +15465,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>moored</t>
+          <t>Moored</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -16455,7 +16455,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stopped</t>
+          <t>Stopped</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>

--- a/dados/SURVEY_STARNAV_D2.xlsx
+++ b/dados/SURVEY_STARNAV_D2.xlsx
@@ -17267,25 +17267,25 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>26.025</v>
+        <v>2.229</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>0</v>
@@ -17329,25 +17329,25 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>26.969</v>
+        <v>1.77</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -17561,21 +17561,21 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>17.389</v>
+        <v>13.95</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -17619,21 +17619,21 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>17.08</v>
+        <v>14.578</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -17677,25 +17677,25 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>27.967</v>
+        <v>0.079</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.1715277777777778</v>
@@ -17735,21 +17735,21 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>17.384</v>
+        <v>13.953</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -17909,21 +17909,21 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>29.618</v>
+        <v>19.1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PNA-1</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Fixa (Habitada)</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>namorado</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -17967,21 +17967,21 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>17.386</v>
+        <v>13.965</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -18025,21 +18025,21 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>17.388</v>
+        <v>13.95</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -18083,21 +18083,21 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>17.388</v>
+        <v>13.95</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -18141,25 +18141,25 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>29.092</v>
+        <v>0.098</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PNA-1</t>
+          <t>PETROBRAS 08 (P-08)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Fixa (Habitada)</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>namorado</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.1673611111111111</v>
@@ -18199,25 +18199,25 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>25.474</v>
+        <v>2.567</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>FPSO CIDADE CAMPOSDOS GOYTACAZES</t>
+          <t>PETROBRAS 65 (P-65)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>FPSO</t>
+          <t>Semi-Sub/Produção</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>tartaruga verde</t>
+          <t>marimbá</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.01180555555555556</v>

--- a/dados/SURVEY_STARNAV_D2.xlsx
+++ b/dados/SURVEY_STARNAV_D2.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46232.76041666666</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.4680555555555556</v>
+      </c>
+      <c r="E20" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.23333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5.937</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>almirante barroso_FSO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1.904166666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1560,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2687,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.004166666666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.63611111111</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.345833333333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PETROBRAS 62 (P-62)(FPSO)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>roncador</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.02847222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -2642,7 +2758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3743,6 +3859,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.377083333333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.427</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -3756,7 +3930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4853,6 +5027,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.66527777778</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.375694444444445</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>57.01666666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NOV Flexiveis</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -4866,7 +5098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5967,6 +6199,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.50208333333</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.213194444444444</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>53.11666666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CIDADE SÃO PAULO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>sapinhoá</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.1652777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -5980,7 +6270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7081,6 +7371,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.66527777778</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.376388888888889</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>57.03333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7094,7 +7442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8195,6 +8543,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.66597222222</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.376388888888889</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>57.03333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -8208,7 +8614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9301,6 +9707,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>111.9666666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>452.688</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>114.3416666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9314,7 +9778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10415,6 +10879,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.02361111111111111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66736111111</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46233.89305555556</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1.624305555555555</v>
+      </c>
+      <c r="E20" t="n">
+        <v>153.17</v>
+      </c>
+      <c r="F20" t="n">
+        <v>57</v>
+      </c>
+      <c r="G20" t="n">
+        <v>38.98333333333333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>61.749</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.7743055555555556</v>
       </c>
     </row>
   </sheetData>
@@ -10428,7 +10950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11529,6 +12051,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46232.58888888889</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.2993055555555555</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.183333333333334</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>3.783</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>P-78</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.075694444444444</v>
       </c>
     </row>
   </sheetData>
@@ -11542,7 +12122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12661,6 +13241,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.01805555555555555</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.47847222222</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.202083333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>10.161</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 43 (P-43)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>barracuda</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.1861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -12674,7 +13312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13775,6 +14413,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.004166666666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46233.78402777778</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1.49375</v>
+      </c>
+      <c r="E20" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>58.535</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.8805555555555555</v>
       </c>
     </row>
   </sheetData>
@@ -13788,7 +14484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14889,6 +15585,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46233.72152777778</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1.429861111111111</v>
+      </c>
+      <c r="E20" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>34.31666666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PNA-1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>namorado</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.9430555555555555</v>
       </c>
     </row>
   </sheetData>
@@ -14902,7 +15656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16015,6 +16769,64 @@
         <v>0.005555555555555556</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.66111111111</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.372222222222222</v>
+      </c>
+      <c r="E21" t="n">
+        <v>243.63</v>
+      </c>
+      <c r="F21" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56.93333333333333</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.874</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.003472222222222222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16026,7 +16838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17107,6 +17919,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.005555555555555556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.63611111111</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.347222222222222</v>
+      </c>
+      <c r="E20" t="n">
+        <v>122.37</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>56.33333333333334</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PETROBRAS 54 (P-54)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>roncador</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.02847222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -17120,7 +17990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18221,6 +19091,64 @@
       </c>
       <c r="P19" s="3" t="n">
         <v>0.01180555555555556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46232.83888888889</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.55625</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.276</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PETROBRAS 08 (P-08)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Produção</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>marimbá</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1.825694444444445</v>
       </c>
     </row>
   </sheetData>
@@ -18234,7 +19162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19281,6 +20209,60 @@
         <v>0.3652777777777778</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46234.66458333333</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.370138888888889</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46234.46458333333</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.535416666666667</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="F20" t="n">
+        <v>56.88333333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>9.852</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>FPSO ANNA NERY</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_STARNAV_D2.xlsx
+++ b/dados/SURVEY_STARNAV_D2.xlsx
@@ -5423,11 +5423,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>23.861</v>
+        <v>1.792</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>FPSO CIDADE MARICA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.01458333333333333</v>
@@ -5481,11 +5481,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>25.833</v>
+        <v>1.044</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>FPSO CIDADE PARATY</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5495,11 +5495,11 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.005555555555555556</v>
@@ -5539,11 +5539,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>19.951</v>
+        <v>0.165</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PETROBRAS 69 (P-69)</t>
+          <t>FPSO CIDADE SAQUAREMA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.1631944444444444</v>
@@ -5597,11 +5597,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>27.406</v>
+        <v>0.703</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>FPSO CIDADE PARATY</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5611,11 +5611,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.02152777777777778</v>
@@ -5655,11 +5655,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>27.406</v>
+        <v>0.703</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>FPSO CIDADE PARATY</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6020833333333333</v>
@@ -5713,11 +5713,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>27.406</v>
+        <v>0.703</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>FPSO CIDADE PARATY</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5727,11 +5727,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.9451388888888889</v>
@@ -5771,11 +5771,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>27.406</v>
+        <v>0.703</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>FPSO CIDADE PARATY</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.604166666666667</v>
@@ -5829,11 +5829,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>27.735</v>
+        <v>1.051</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FPSO CARIOCA MV30</t>
+          <t>FPSO CIDADE PARATY</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5843,11 +5843,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>sepia</t>
+          <t>tupi</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.06388888888888888</v>

--- a/dados/SURVEY_STARNAV_D2.xlsx
+++ b/dados/SURVEY_STARNAV_D2.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1605,6 +1605,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>1.904166666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.4</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.639583333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>202.37</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -1618,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2549,25 +2607,21 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5.228</v>
+        <v>4.48</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>TIDAL ACTION(Navio Sonda)</t>
+          <t>NORBE VIII (NS 32)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>navio sonda</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>roncador</t>
-        </is>
-      </c>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.1805555555555556</v>
@@ -2745,6 +2799,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.02847222222222222</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46234.63611111111</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 62 (P-62)(FPSO)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>roncador</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.7673611111111112</v>
       </c>
     </row>
   </sheetData>
@@ -2758,7 +2870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3917,6 +4029,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.39583333334</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.73125</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.378</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -3930,7 +4100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5085,6 +5255,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.06805555556</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.4027777777777778</v>
+      </c>
+      <c r="E21" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>30.004</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>TechnipFMC Flexiveis</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.3326388888888889</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6257,6 +6485,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.1652777777777778</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.39236111111</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.8902777777777777</v>
+      </c>
+      <c r="E21" t="n">
+        <v>240.65</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21.36666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>83.366</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.008333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -6270,7 +6556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7429,6 +7715,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.39722222222</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.7319444444444444</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>17.56666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.003472222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -7442,7 +7786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8601,6 +8945,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.39583333334</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.7298611111111111</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>17.51666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -8614,7 +9016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9765,6 +10167,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>114.3416666666667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>452.688</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>115.075</v>
       </c>
     </row>
   </sheetData>
@@ -9778,7 +10238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10937,6 +11397,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.7743055555555556</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46233.89305555556</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>61.749</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.507638888888889</v>
       </c>
     </row>
   </sheetData>
@@ -10950,7 +11468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12109,6 +12627,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>2.075694444444444</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.38888888889</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>96.26000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>76.413</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>P-79</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.01458333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -12122,7 +12698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13299,6 +13875,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.1861111111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9222222222222223</v>
+      </c>
+      <c r="E22" t="n">
+        <v>115.99</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>22.13333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NOV Flexiveis</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.002777777777777778</v>
       </c>
     </row>
   </sheetData>
@@ -13312,7 +13946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14471,6 +15105,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.8805555555555555</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46233.78402777778</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>58.535</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.619444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -14484,7 +15176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15643,6 +16335,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9430555555555555</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.11736111111</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1.395833333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PNA-1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>namorado</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.2861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -15656,7 +16406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16827,6 +17577,64 @@
         <v>0.003472222222222222</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.40138888889</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.7402777777777778</v>
+      </c>
+      <c r="E22" t="n">
+        <v>65.86</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>17.76666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>61.654</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16838,7 +17646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17727,25 +18535,21 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>3.716</v>
+        <v>1.279</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>LAGUNA STAR (NS44)</t>
+          <t>NORBE VIII (NS 32)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>navio sonda</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>roncador</t>
-        </is>
-      </c>
+          <t>Semi-Sub/Perfuração</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>0.0006944444444444445</v>
@@ -17977,6 +18781,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>0.02847222222222222</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.36944444444</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PETROBRAS 54 (P-54)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>roncador</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.03402777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -17990,7 +18852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19149,6 +20011,64 @@
       </c>
       <c r="P20" s="3" t="n">
         <v>1.825694444444445</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.40208333333</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.563194444444445</v>
+      </c>
+      <c r="E21" t="n">
+        <v>103.16</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>61.51666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NOV Flexiveis</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -19162,7 +20082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20263,6 +21183,60 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0.7388888888888889</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46235.30625</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.73333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FPSO ANITA GARIBALDI(MV 33)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0.09722222222222222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_STARNAV_D2.xlsx
+++ b/dados/SURVEY_STARNAV_D2.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,6 +1663,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.36111111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.004166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1676,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2857,6 +2915,60 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.7673611111111112</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.34930555556</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1.713194444444444</v>
+      </c>
+      <c r="E22" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>41.11666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>25.331</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FSO CIDADE DE MACAÉ MV 15 (PSME)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.01597222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -2870,7 +2982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4087,6 +4199,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36319444444</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.36111111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9652777777777778</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.16666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -4100,7 +4270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5313,6 +5483,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.3326388888888889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36319444444</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.03472222222</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="E22" t="n">
+        <v>166.89</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>4.148</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>VALARIS DS-17</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>raia</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.3284722222222222</v>
       </c>
     </row>
   </sheetData>
@@ -5326,7 +5554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6771,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.008333333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36319444444</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.36111111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="E22" t="n">
+        <v>88.79000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -6556,7 +6842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7773,6 +8059,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.003472222222222222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36319444444</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.36180555556</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9645833333333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -7786,7 +8130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9003,6 +9347,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.004861111111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36319444444</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.36180555556</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9659722222222222</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.18333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -9016,7 +9418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10225,6 +10627,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>115.075</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36319444444</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>452.688</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>116.0375</v>
       </c>
     </row>
   </sheetData>
@@ -10238,7 +10698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11455,6 +11915,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1.507638888888889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36319444444</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.36180555556</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.46875</v>
+      </c>
+      <c r="E22" t="n">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.001388888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -11468,7 +11986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12685,6 +13203,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.01458333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.36111111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="E22" t="n">
+        <v>123.95</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.004166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -12698,7 +13274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13933,6 +14509,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.002777777777777778</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.13194444445</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.73125</v>
+      </c>
+      <c r="E23" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>5.835</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FPSO PARGO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>pargo</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.2333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -13946,7 +14580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15163,6 +15797,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>1.619444444444444</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46233.78402777778</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>58.535</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Niterói</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.58125</v>
       </c>
     </row>
   </sheetData>
@@ -15176,7 +15868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16393,6 +17085,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2861111111111111</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.03541666667</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9180555555555555</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>22.03333333333333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2.679</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PGP-1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>garoupa</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.3298611111111111</v>
       </c>
     </row>
   </sheetData>
@@ -16406,7 +17156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17635,6 +18385,64 @@
         <v>0.002083333333333333</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.35833333333</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9569444444444445</v>
+      </c>
+      <c r="E23" t="n">
+        <v>209.74</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.96666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR ACX</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.006944444444444444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17646,7 +18454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18839,6 +19647,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.03402777777777777</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.34652777778</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.9770833333333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>35.681</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PGP-1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>garoupa</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.01875</v>
       </c>
     </row>
   </sheetData>
@@ -18852,7 +19718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20069,6 +20935,64 @@
       </c>
       <c r="P21" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46236.28611111111</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.8840277777777777</v>
+      </c>
+      <c r="E22" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>21.21666666666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>16.401</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>BR ACX</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.07916666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -20082,7 +21006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21237,6 +22161,60 @@
         <v>0.09722222222222222</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46236.36527777778</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0.9618055555555556</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46235.70972222222</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.4034722222222222</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23.08333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.683333333333334</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FPSO ANITA GARIBALDI(MV 33)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.6555555555555556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dados/SURVEY_STARNAV_D2.xlsx
+++ b/dados/SURVEY_STARNAV_D2.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,6 +1721,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.004166666666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9604166666666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2969,6 +3027,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.01597222222222222</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.30833333333</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9590277777777778</v>
+      </c>
+      <c r="E23" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.01666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>10.821</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PETROBRAS 54 (P-54)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>roncador</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.01805555555555555</v>
       </c>
     </row>
   </sheetData>
@@ -2982,7 +3098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4257,6 +4373,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9631944444444445</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9604166666666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.11666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Rio</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Baker Hughes Planta de Fluídos - Rio</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -4270,7 +4444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5541,6 +5715,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.3284722222222222</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9631944444444445</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.30902777778</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.274305555555556</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.11666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30.58333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>8.148999999999999</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>VALARIS DS-17</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>raia</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.01736111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -5554,7 +5786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6829,6 +7061,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.002083333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9631944444444445</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9604166666666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.11666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.004861111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -6842,7 +7132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8117,6 +8407,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9631944444444445</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.32222222222</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9604166666666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.11666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.004166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8130,7 +8478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9405,6 +9753,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9631944444444445</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.32222222222</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9604166666666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.11666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.004166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -9418,7 +9824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10685,6 +11091,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>116.0375</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9631944444444445</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46120.32569444444</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.11666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>452.688</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NS 54 (VALARIS DS 4)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>navio sonda</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>exploração desconhecida</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>117.0006944444444</v>
       </c>
     </row>
   </sheetData>
@@ -10698,7 +11162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11973,6 +12437,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.001388888888888889</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9631944444444445</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.31875</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9569444444444445</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.11666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.96666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BR RIO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Fundeio - RIO</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.007638888888888889</v>
       </c>
     </row>
   </sheetData>
@@ -11986,7 +12508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13261,6 +13783,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.004166666666666667</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.31666666667</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22.93333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Triunfo Logística</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.009722222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -13274,7 +13854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14567,6 +15147,60 @@
       </c>
       <c r="P23" s="3" t="n">
         <v>0.2333333333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.31736111111</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1.185416666666667</v>
+      </c>
+      <c r="E24" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>FPSO ANNA NERY</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.009027777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -14580,7 +15214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15855,6 +16489,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>2.58125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.91458333333</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>3.130555555555556</v>
+      </c>
+      <c r="E23" t="n">
+        <v>140.18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>75.13333333333334</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3.453</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>P-79</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FPSO</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>buzios</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.4118055555555555</v>
       </c>
     </row>
   </sheetData>
@@ -15868,7 +16560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17143,6 +17835,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.3298611111111111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.288888888888889</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30.93333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PNA-1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Fixa (Habitada)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>namorado</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -17156,7 +17906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18443,6 +19193,64 @@
         <v>0.006944444444444444</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46237.32569444444</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.9673611111111111</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23.21666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR ACX</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18454,7 +19262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19705,6 +20513,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.01875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.46666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>42.931</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>TechnipFMC Flexiveis</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>porto açu</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.002083333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -19718,7 +20584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20993,6 +21859,64 @@
       </c>
       <c r="P22" s="3" t="n">
         <v>0.07916666666666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46237.31944444445</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="E23" t="n">
+        <v>93.42</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PETROBRAS 65 (P-65)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Produção</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>marimbá</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.006944444444444444</v>
       </c>
     </row>
   </sheetData>
@@ -21006,7 +21930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22215,6 +23139,64 @@
         <v>0.6555555555555556</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46237.32638888889</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9611111111111111</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46236.53194444445</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.8222222222222222</v>
+      </c>
+      <c r="E23" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.06666666666667</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19.73333333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PETROBRAS 56 (P-56)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Semi-Sub/Produção</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>marlin sul</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.7944444444444444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
